--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC06DB35-08BD-409F-AF35-70B310DFB693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A4A08D-AC35-4751-A153-25C7B45FDD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A4A08D-AC35-4751-A153-25C7B45FDD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BE1C0E-FD1F-4203-BC98-3DE8A7492576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BE1C0E-FD1F-4203-BC98-3DE8A7492576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF2ADEF-F6FC-466C-A1B2-7692319F0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,7 +618,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3">
         <v>18</v>
@@ -650,10 +650,10 @@
         <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3">
         <v>18</v>
@@ -665,7 +665,7 @@
         <v>23</v>
       </c>
       <c r="I4" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J4" s="4">
         <v>78</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>20</v>
@@ -1002,16 +1002,16 @@
         <v>6</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3">
         <v>9</v>
@@ -1020,18 +1020,18 @@
         <v>-2</v>
       </c>
       <c r="J15" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -1042,8 +1042,8 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1">
-        <v>6</v>
+      <c r="G16" s="3">
+        <v>8</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1052,12 +1052,12 @@
         <v>-1</v>
       </c>
       <c r="J16" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF2ADEF-F6FC-466C-A1B2-7692319F0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00EDAAB-1E07-4324-B172-8E8993FF5766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,8 +617,8 @@
       <c r="C3" s="2">
         <v>14</v>
       </c>
-      <c r="D3" s="2">
-        <v>16</v>
+      <c r="D3" s="1">
+        <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>18</v>
@@ -1065,7 +1065,7 @@
       <c r="C17" s="1">
         <v>6</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="1">
         <v>4</v>
       </c>
       <c r="E17" s="1">

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00EDAAB-1E07-4324-B172-8E8993FF5766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892336A2-7940-47BF-8692-D1741B28470E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>排名</t>
   </si>
@@ -615,28 +615,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3">
         <v>18</v>
       </c>
       <c r="F3" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1">
         <v>-4</v>
       </c>
       <c r="J3" s="4">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -673,25 +673,25 @@
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3">
         <v>21</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -711,28 +711,28 @@
         <v>14</v>
       </c>
       <c r="C6" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="J6" s="1">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -743,28 +743,28 @@
         <v>15</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10</v>
       </c>
       <c r="F7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J7" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -775,28 +775,28 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1">
-        <v>7</v>
+      <c r="H8" s="3">
+        <v>10</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J8" s="1">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -807,28 +807,28 @@
         <v>17</v>
       </c>
       <c r="C9" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H9" s="3">
         <v>22</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="4">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -871,28 +871,28 @@
         <v>19</v>
       </c>
       <c r="C11" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
         <v>18</v>
       </c>
       <c r="E11" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H11" s="1">
         <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J11" s="4">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -929,34 +929,34 @@
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1">
-        <v>7</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>8</v>
       </c>
       <c r="F13" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H13" s="1">
         <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J13" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -993,7 +993,7 @@
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>23</v>
@@ -1042,7 +1042,7 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="1">
         <v>8</v>
       </c>
       <c r="H16" s="1">
@@ -1057,39 +1057,39 @@
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J17" s="5">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
@@ -1128,9 +1128,586 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1">
+        <v>-2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1">
+        <v>-4</v>
+      </c>
+      <c r="J3" s="4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1">
+        <v>-4</v>
+      </c>
+      <c r="J4" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-6</v>
+      </c>
+      <c r="J6" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>18</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>57</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>15</v>
+      </c>
+      <c r="H9" s="3">
+        <v>22</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-3</v>
+      </c>
+      <c r="J10" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1">
+        <v>-4</v>
+      </c>
+      <c r="J11" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-4</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-3</v>
+      </c>
+      <c r="J13" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>12</v>
+      </c>
+      <c r="H15" s="3">
+        <v>9</v>
+      </c>
+      <c r="I15" s="1">
+        <v>-2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>10</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>15</v>
+      </c>
+      <c r="G17" s="3">
+        <v>15</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="2">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>24</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892336A2-7940-47BF-8692-D1741B28470E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626BA6C9-422F-487B-81BE-FB218B9CB79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,13 +583,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1">
         <v>9</v>
       </c>
       <c r="E2" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -604,7 +604,7 @@
         <v>-2</v>
       </c>
       <c r="J2" s="4">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -641,19 +641,19 @@
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3">
         <v>18</v>
@@ -668,7 +668,7 @@
         <v>-4</v>
       </c>
       <c r="J4" s="4">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -679,28 +679,28 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H5" s="3">
         <v>21</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="4">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -737,34 +737,34 @@
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="1">
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J7" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -874,13 +874,13 @@
         <v>14</v>
       </c>
       <c r="D11" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
       </c>
       <c r="F11" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3">
         <v>28</v>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J11" s="4">
         <v>64</v>
@@ -906,10 +906,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -924,18 +924,18 @@
         <v>-4</v>
       </c>
       <c r="J12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1">
         <v>8</v>
@@ -944,19 +944,19 @@
         <v>8</v>
       </c>
       <c r="F13" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" s="3">
         <v>11</v>
       </c>
       <c r="H13" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J13" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1013,7 +1013,7 @@
       <c r="G15" s="3">
         <v>12</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="1">
         <v>9</v>
       </c>
       <c r="I15" s="1">
@@ -1031,92 +1031,92 @@
         <v>24</v>
       </c>
       <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1">
         <v>2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J16" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
       </c>
       <c r="E17" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J17" s="5">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>24</v>
-      </c>
-      <c r="G18" s="1">
-        <v>6</v>
+        <v>26</v>
+      </c>
+      <c r="G18" s="3">
+        <v>11</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J18" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1203,28 +1203,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>18</v>
       </c>
       <c r="F3" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3">
         <v>18</v>
-      </c>
-      <c r="H3" s="3">
-        <v>20</v>
       </c>
       <c r="I3" s="1">
         <v>-4</v>
       </c>
       <c r="J3" s="4">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1261,25 +1261,25 @@
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3">
         <v>21</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1299,28 +1299,28 @@
         <v>14</v>
       </c>
       <c r="C6" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3">
         <v>14</v>
       </c>
-      <c r="E6" s="3">
-        <v>18</v>
-      </c>
       <c r="F6" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J6" s="1">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1331,28 +1331,28 @@
         <v>15</v>
       </c>
       <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="1">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3">
-        <v>10</v>
+      <c r="E7" s="1">
+        <v>5</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1363,28 +1363,28 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>7</v>
       </c>
-      <c r="E8" s="3">
-        <v>18</v>
-      </c>
-      <c r="F8" s="3">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>10</v>
-      </c>
       <c r="I8" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1395,28 +1395,28 @@
         <v>17</v>
       </c>
       <c r="C9" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3">
         <v>22</v>
       </c>
       <c r="I9" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1459,28 +1459,28 @@
         <v>19</v>
       </c>
       <c r="C11" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2">
         <v>18</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H11" s="1">
         <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J11" s="4">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1517,34 +1517,34 @@
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3">
         <v>9</v>
       </c>
-      <c r="D13" s="1">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>11</v>
-      </c>
       <c r="G13" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H13" s="1">
         <v>5</v>
       </c>
       <c r="I13" s="1">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J13" s="1">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>23</v>
@@ -1630,7 +1630,7 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
         <v>8</v>
       </c>
       <c r="H16" s="1">
@@ -1645,39 +1645,39 @@
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="5">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626BA6C9-422F-487B-81BE-FB218B9CB79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BD373B-8717-41F7-B450-D0332FD111F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>排名</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>大喷菇（吴成玮）</t>
+  </si>
+  <si>
+    <t>荷叶（卢晨）</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
@@ -583,19 +586,19 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3">
         <v>13</v>
@@ -604,7 +607,7 @@
         <v>-2</v>
       </c>
       <c r="J2" s="4">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -615,28 +618,28 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="D3" s="2">
+        <v>11</v>
       </c>
       <c r="E3" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J3" s="4">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -647,28 +650,28 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3">
         <v>22</v>
       </c>
       <c r="H4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J4" s="4">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -679,28 +682,28 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="1">
         <v>-1</v>
       </c>
       <c r="J5" s="4">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -769,7 +772,7 @@
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
@@ -810,13 +813,13 @@
         <v>26</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3">
         <v>15</v>
@@ -828,7 +831,7 @@
         <v>-1</v>
       </c>
       <c r="J9" s="4">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -839,28 +842,28 @@
         <v>18</v>
       </c>
       <c r="C10" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
       </c>
       <c r="F10" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
       </c>
       <c r="I10" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J10" s="4">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -886,13 +889,13 @@
         <v>28</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="1">
         <v>-5</v>
       </c>
       <c r="J11" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -934,17 +937,17 @@
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="1">
-        <v>10</v>
+      <c r="C13" s="2">
+        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>8</v>
       </c>
-      <c r="E13" s="1">
-        <v>8</v>
+      <c r="E13" s="3">
+        <v>10</v>
       </c>
       <c r="F13" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" s="3">
         <v>11</v>
@@ -953,10 +956,10 @@
         <v>6</v>
       </c>
       <c r="I13" s="1">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J13" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
@@ -1013,7 +1016,7 @@
       <c r="G15" s="3">
         <v>12</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="3">
         <v>9</v>
       </c>
       <c r="I15" s="1">
@@ -1024,10 +1027,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="1">
@@ -1042,7 +1045,7 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="3">
         <v>9</v>
       </c>
       <c r="H16" s="1">
@@ -1056,10 +1059,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>9</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="1">
@@ -1083,13 +1086,13 @@
       <c r="I17" s="1">
         <v>-2</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="1">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
@@ -1098,16 +1101,16 @@
         <v>8</v>
       </c>
       <c r="D18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1116,7 +1119,39 @@
         <v>-4</v>
       </c>
       <c r="J18" s="1">
-        <v>36</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/auto_jifen.xlsx
+++ b/auto_jifen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vsco_file\hex_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BD373B-8717-41F7-B450-D0332FD111F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22050178-FB08-48C3-80E1-46E058500E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,13 +633,13 @@
         <v>20</v>
       </c>
       <c r="H3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1">
         <v>-5</v>
       </c>
       <c r="J3" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
